--- a/data/trans_camb/P36B08_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22,53</t>
+          <t>22,85</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,06</t>
+          <t>18,19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,32</t>
+          <t>20,54</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 7,9</t>
+          <t>-1,73; 7,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 6,6</t>
+          <t>-3,44; 6,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,34; 26,48</t>
+          <t>19,06; 26,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 8,92</t>
+          <t>0,42; 9,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 2,66</t>
+          <t>-6,74; 1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,79; 21,91</t>
+          <t>14,9; 21,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 7,52</t>
+          <t>0,92; 7,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,82</t>
+          <t>-3,39; 3,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 23,04</t>
+          <t>18,06; 23,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 11,52</t>
+          <t>-2,26; 10,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 9,45</t>
+          <t>-4,65; 9,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,18; 38,16</t>
+          <t>25,49; 38,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 11,76</t>
+          <t>0,53; 11,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 3,46</t>
+          <t>-8,46; 2,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 29,46</t>
+          <t>18,52; 28,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 10,18</t>
+          <t>1,13; 9,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,8</t>
+          <t>-4,41; 4,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 31,74</t>
+          <t>23,53; 31,72</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33,93</t>
+          <t>33,36</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,32</t>
+          <t>28,47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>31,06</t>
+          <t>30,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 12,86</t>
+          <t>4,39; 12,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 14,23</t>
+          <t>5,6; 14,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,28; 38,07</t>
+          <t>29,84; 36,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,14</t>
+          <t>4,82; 12,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 11,85</t>
+          <t>4,14; 12,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,43; 31,55</t>
+          <t>25,4; 32,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 11,43</t>
+          <t>5,53; 11,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 11,55</t>
+          <t>6,02; 11,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,83; 33,68</t>
+          <t>28,6; 33,49</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 21,82</t>
+          <t>6,81; 21,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,96; 23,7</t>
+          <t>8,53; 23,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,73; 65,01</t>
+          <t>45,57; 62,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 18,38</t>
+          <t>6,8; 19,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 18,01</t>
+          <t>5,92; 18,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,39; 47,91</t>
+          <t>35,45; 48,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 17,98</t>
+          <t>8,24; 18,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 18,27</t>
+          <t>9,08; 18,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,73; 53,12</t>
+          <t>42,48; 53,11</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34,67</t>
+          <t>35,13</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,38</t>
+          <t>23,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29,66</t>
+          <t>29,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 13,64</t>
+          <t>3,0; 13,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 13,83</t>
+          <t>3,01; 13,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,21; 39,18</t>
+          <t>30,8; 39,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 8,5</t>
+          <t>-0,71; 8,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,42</t>
+          <t>-2,07; 7,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,14; 29,06</t>
+          <t>19,49; 27,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,95</t>
+          <t>2,77; 9,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,11</t>
+          <t>2,42; 9,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,96; 32,68</t>
+          <t>26,53; 32,37</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,0; 24,84</t>
+          <t>4,85; 24,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 25,14</t>
+          <t>5,0; 25,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49,19; 72,37</t>
+          <t>50,28; 72,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 12,69</t>
+          <t>-0,94; 12,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 10,98</t>
+          <t>-2,82; 10,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,44; 43,11</t>
+          <t>26,64; 40,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 16,01</t>
+          <t>4,21; 15,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 14,73</t>
+          <t>3,83; 14,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,44; 53,15</t>
+          <t>39,89; 52,28</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31,97</t>
+          <t>32,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,58</t>
+          <t>26,33</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29,18</t>
+          <t>29,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,13</t>
+          <t>6,9; 15,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,05; 18,46</t>
+          <t>10,2; 18,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,7; 35,69</t>
+          <t>28,36; 35,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,6; 18,08</t>
+          <t>10,54; 18,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,15</t>
+          <t>9,69; 17,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,76; 30,24</t>
+          <t>23,51; 29,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,71; 15,42</t>
+          <t>9,84; 15,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,97; 16,71</t>
+          <t>11,31; 16,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,61; 31,58</t>
+          <t>26,9; 31,43</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 25,62</t>
+          <t>10,93; 25,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,85; 31,15</t>
+          <t>16,23; 31,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,91; 61,15</t>
+          <t>44,62; 60,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,77; 26,99</t>
+          <t>14,84; 27,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,99; 25,81</t>
+          <t>13,58; 25,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,14; 45,8</t>
+          <t>32,67; 44,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,49; 24,4</t>
+          <t>14,68; 24,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,31; 26,27</t>
+          <t>16,92; 26,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39,49; 49,59</t>
+          <t>39,93; 49,51</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>31,14</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,82</t>
+          <t>24,65</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>27,97</t>
+          <t>27,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,38</t>
+          <t>5,5; 10,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,44</t>
+          <t>6,89; 11,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,28; 33,31</t>
+          <t>28,99; 33,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,49</t>
+          <t>6,31; 10,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,41</t>
+          <t>3,95; 8,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,11; 26,45</t>
+          <t>22,95; 26,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,7</t>
+          <t>6,61; 9,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,29</t>
+          <t>6,0; 9,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26,62; 29,41</t>
+          <t>26,63; 29,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,67; 16,76</t>
+          <t>8,57; 16,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10,68; 18,54</t>
+          <t>10,57; 18,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45,2; 53,98</t>
+          <t>44,77; 53,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,59; 14,97</t>
+          <t>8,67; 14,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,01</t>
+          <t>5,5; 11,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,92; 37,86</t>
+          <t>31,67; 37,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,72; 14,62</t>
+          <t>9,72; 14,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,92; 14,04</t>
+          <t>8,85; 13,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>39,09; 44,47</t>
+          <t>39,03; 44,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P36B08_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
